--- a/main/ig/StructureDefinition-dmi-organization-interne.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-interne.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-organization-interne.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-interne.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-organization-interne.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-interne.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6590" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1678,6 +1678,9 @@
   </si>
   <si>
     <t>Organization.type:TypeOrganizationInterne.coding.code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Organization.type:TypeOrganizationInterne.coding.display</t>
@@ -18388,7 +18391,7 @@
         <v>79</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>116</v>
@@ -18397,7 +18400,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18504,7 +18507,7 @@
         <v>79</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>99</v>
@@ -18730,7 +18733,7 @@
         <v>79</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>116</v>
@@ -18739,7 +18742,7 @@
         <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
@@ -18846,7 +18849,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -18960,7 +18963,7 @@
         <v>87</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>99</v>
@@ -19014,7 +19017,9 @@
       <c r="M146" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N146" s="2"/>
+      <c r="N146" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O146" t="s" s="2">
         <v>386</v>
       </c>
@@ -19074,7 +19079,7 @@
         <v>87</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>99</v>
@@ -19094,7 +19099,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>489</v>
@@ -19128,7 +19133,9 @@
       <c r="M147" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N147" s="2"/>
+      <c r="N147" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O147" t="s" s="2">
         <v>394</v>
       </c>
@@ -19188,7 +19195,7 @@
         <v>87</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19208,7 +19215,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>491</v>
@@ -19304,7 +19311,7 @@
         <v>87</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>99</v>
@@ -19324,7 +19331,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>493</v>
@@ -19420,7 +19427,7 @@
         <v>87</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>99</v>
@@ -19440,13 +19447,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>457</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>77</v>
@@ -19558,7 +19565,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>472</v>
@@ -19670,7 +19677,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>474</v>
@@ -19764,7 +19771,7 @@
         <v>79</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>116</v>
@@ -19773,7 +19780,7 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
@@ -19784,7 +19791,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>476</v>
@@ -19880,7 +19887,7 @@
         <v>79</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>99</v>
@@ -19900,7 +19907,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>478</v>
@@ -20012,7 +20019,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>480</v>
@@ -20106,7 +20113,7 @@
         <v>79</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>116</v>
@@ -20115,7 +20122,7 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
@@ -20126,7 +20133,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>482</v>
@@ -20174,7 +20181,7 @@
         <v>77</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>77</v>
@@ -20222,7 +20229,7 @@
         <v>87</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>99</v>
@@ -20242,7 +20249,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>484</v>
@@ -20336,7 +20343,7 @@
         <v>87</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>99</v>
@@ -20356,7 +20363,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>486</v>
@@ -20390,7 +20397,9 @@
       <c r="M158" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N158" s="2"/>
+      <c r="N158" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O158" t="s" s="2">
         <v>386</v>
       </c>
@@ -20450,7 +20459,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -20470,7 +20479,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>489</v>
@@ -20504,7 +20513,9 @@
       <c r="M159" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N159" s="2"/>
+      <c r="N159" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O159" t="s" s="2">
         <v>394</v>
       </c>
@@ -20564,7 +20575,7 @@
         <v>87</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>99</v>
@@ -20584,7 +20595,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>491</v>
@@ -20680,7 +20691,7 @@
         <v>87</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>99</v>
@@ -20700,7 +20711,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>493</v>
@@ -20796,7 +20807,7 @@
         <v>87</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>99</v>
@@ -20816,10 +20827,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20845,16 +20856,16 @@
         <v>101</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20903,7 +20914,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20918,13 +20929,13 @@
         <v>99</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>77</v>
@@ -20932,10 +20943,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20961,16 +20972,16 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -21019,7 +21030,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21037,7 +21048,7 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -21048,10 +21059,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21074,19 +21085,19 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21135,7 +21146,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21147,16 +21158,16 @@
         <v>199</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>77</v>
@@ -21164,10 +21175,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21190,19 +21201,19 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21251,7 +21262,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21263,16 +21274,16 @@
         <v>199</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>77</v>
@@ -21280,10 +21291,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21306,17 +21317,17 @@
         <v>88</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21365,7 +21376,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21383,7 +21394,7 @@
         <v>453</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>105</v>
@@ -21394,10 +21405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21506,10 +21517,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21620,10 +21631,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21649,13 +21660,13 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21705,7 +21716,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21714,7 +21725,7 @@
         <v>87</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>99</v>
@@ -21734,10 +21745,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21763,13 +21774,13 @@
         <v>129</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21817,7 +21828,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -21846,10 +21857,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21875,13 +21886,13 @@
         <v>229</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -21931,7 +21942,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21949,7 +21960,7 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
@@ -21960,10 +21971,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21989,13 +22000,13 @@
         <v>101</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22045,7 +22056,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22074,10 +22085,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22100,19 +22111,19 @@
         <v>77</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -22161,7 +22172,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22179,7 +22190,7 @@
         <v>77</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>77</v>
@@ -22190,10 +22201,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22302,10 +22313,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22416,14 +22427,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -22445,10 +22456,10 @@
         <v>108</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>111</v>
@@ -22503,7 +22514,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -22532,10 +22543,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22561,14 +22572,14 @@
         <v>252</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -22596,10 +22607,10 @@
         <v>149</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>77</v>
@@ -22617,7 +22628,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -22635,7 +22646,7 @@
         <v>77</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>77</v>
@@ -22646,10 +22657,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22672,17 +22683,17 @@
         <v>77</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>77</v>
@@ -22731,7 +22742,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -22746,10 +22757,10 @@
         <v>99</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>77</v>
@@ -22760,10 +22771,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22786,17 +22797,17 @@
         <v>77</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -22845,7 +22856,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -22857,16 +22868,16 @@
         <v>199</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>77</v>
@@ -22874,10 +22885,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22900,19 +22911,19 @@
         <v>77</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -22961,7 +22972,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -22976,13 +22987,13 @@
         <v>99</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>77</v>
@@ -22990,10 +23001,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23016,17 +23027,17 @@
         <v>77</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -23075,7 +23086,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-dmi-organization-interne.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-interne.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6590" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1678,9 +1678,6 @@
   </si>
   <si>
     <t>Organization.type:TypeOrganizationInterne.coding.code</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Organization.type:TypeOrganizationInterne.coding.display</t>
@@ -18391,7 +18388,7 @@
         <v>79</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>116</v>
@@ -18400,7 +18397,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18507,7 +18504,7 @@
         <v>79</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>99</v>
@@ -18733,7 +18730,7 @@
         <v>79</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>116</v>
@@ -18742,7 +18739,7 @@
         <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
@@ -18849,7 +18846,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -18963,7 +18960,7 @@
         <v>87</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>99</v>
@@ -19017,9 +19014,7 @@
       <c r="M146" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N146" t="s" s="2">
-        <v>535</v>
-      </c>
+      <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
         <v>386</v>
       </c>
@@ -19079,7 +19074,7 @@
         <v>87</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>99</v>
@@ -19099,7 +19094,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>489</v>
@@ -19133,9 +19128,7 @@
       <c r="M147" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N147" t="s" s="2">
-        <v>535</v>
-      </c>
+      <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
         <v>394</v>
       </c>
@@ -19195,7 +19188,7 @@
         <v>87</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19215,7 +19208,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>491</v>
@@ -19311,7 +19304,7 @@
         <v>87</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>99</v>
@@ -19331,7 +19324,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>493</v>
@@ -19427,7 +19420,7 @@
         <v>87</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>99</v>
@@ -19447,13 +19440,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>457</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>77</v>
@@ -19565,7 +19558,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>472</v>
@@ -19677,7 +19670,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>474</v>
@@ -19771,7 +19764,7 @@
         <v>79</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>116</v>
@@ -19780,7 +19773,7 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
@@ -19791,7 +19784,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>476</v>
@@ -19887,7 +19880,7 @@
         <v>79</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>99</v>
@@ -19907,7 +19900,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>478</v>
@@ -20019,7 +20012,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>480</v>
@@ -20113,7 +20106,7 @@
         <v>79</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>116</v>
@@ -20122,7 +20115,7 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
@@ -20133,7 +20126,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>482</v>
@@ -20181,7 +20174,7 @@
         <v>77</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>77</v>
@@ -20229,7 +20222,7 @@
         <v>87</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>99</v>
@@ -20249,7 +20242,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>484</v>
@@ -20343,7 +20336,7 @@
         <v>87</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>99</v>
@@ -20363,7 +20356,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>486</v>
@@ -20397,9 +20390,7 @@
       <c r="M158" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N158" t="s" s="2">
-        <v>535</v>
-      </c>
+      <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
         <v>386</v>
       </c>
@@ -20459,7 +20450,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -20479,7 +20470,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>489</v>
@@ -20513,9 +20504,7 @@
       <c r="M159" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N159" t="s" s="2">
-        <v>535</v>
-      </c>
+      <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
         <v>394</v>
       </c>
@@ -20575,7 +20564,7 @@
         <v>87</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>99</v>
@@ -20595,7 +20584,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>491</v>
@@ -20691,7 +20680,7 @@
         <v>87</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>99</v>
@@ -20711,7 +20700,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>493</v>
@@ -20807,7 +20796,7 @@
         <v>87</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>99</v>
@@ -20827,10 +20816,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20856,16 +20845,16 @@
         <v>101</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="N162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20914,7 +20903,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20929,13 +20918,13 @@
         <v>99</v>
       </c>
       <c r="AK162" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL162" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AL162" t="s" s="2">
+      <c r="AM162" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>77</v>
@@ -20943,10 +20932,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20972,16 +20961,16 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -21030,7 +21019,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21048,7 +21037,7 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -21059,10 +21048,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21085,19 +21074,19 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21146,7 +21135,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21158,16 +21147,16 @@
         <v>199</v>
       </c>
       <c r="AJ164" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AK164" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AK164" t="s" s="2">
+      <c r="AL164" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AL164" t="s" s="2">
+      <c r="AM164" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>77</v>
@@ -21175,10 +21164,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21201,19 +21190,19 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="M165" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21262,7 +21251,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21274,16 +21263,16 @@
         <v>199</v>
       </c>
       <c r="AJ165" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AK165" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AK165" t="s" s="2">
+      <c r="AL165" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="AL165" t="s" s="2">
+      <c r="AM165" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>77</v>
@@ -21291,10 +21280,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21317,17 +21306,17 @@
         <v>88</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="L166" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="M166" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21376,7 +21365,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21394,7 +21383,7 @@
         <v>453</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>105</v>
@@ -21405,10 +21394,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21517,10 +21506,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21631,10 +21620,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21660,13 +21649,13 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21716,16 +21705,16 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI169" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>99</v>
@@ -21745,10 +21734,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21774,13 +21763,13 @@
         <v>129</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21828,7 +21817,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -21857,10 +21846,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21886,13 +21875,13 @@
         <v>229</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -21942,7 +21931,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21960,7 +21949,7 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
@@ -21971,10 +21960,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22000,13 +21989,13 @@
         <v>101</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22056,7 +22045,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22085,10 +22074,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22111,19 +22100,19 @@
         <v>77</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L173" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L173" t="s" s="2">
+      <c r="M173" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -22172,7 +22161,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22190,7 +22179,7 @@
         <v>77</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>77</v>
@@ -22201,10 +22190,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22313,10 +22302,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22427,14 +22416,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -22456,10 +22445,10 @@
         <v>108</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>111</v>
@@ -22514,7 +22503,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -22543,10 +22532,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22572,14 +22561,14 @@
         <v>252</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -22607,11 +22596,11 @@
         <v>149</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="Z177" t="s" s="2">
-        <v>635</v>
-      </c>
       <c r="AA177" t="s" s="2">
         <v>77</v>
       </c>
@@ -22628,7 +22617,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -22646,7 +22635,7 @@
         <v>77</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>77</v>
@@ -22657,10 +22646,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22683,17 +22672,17 @@
         <v>77</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>77</v>
@@ -22742,7 +22731,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -22757,10 +22746,10 @@
         <v>99</v>
       </c>
       <c r="AK178" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AL178" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AL178" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>77</v>
@@ -22771,10 +22760,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22797,17 +22786,17 @@
         <v>77</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -22856,7 +22845,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -22868,16 +22857,16 @@
         <v>199</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AK179" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AL179" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AL179" t="s" s="2">
+      <c r="AM179" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>77</v>
@@ -22885,10 +22874,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22911,19 +22900,19 @@
         <v>77</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N180" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="O180" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -22972,7 +22961,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -22987,13 +22976,13 @@
         <v>99</v>
       </c>
       <c r="AK180" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AL180" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="AL180" t="s" s="2">
+      <c r="AM180" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>77</v>
@@ -23001,10 +22990,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23027,17 +23016,17 @@
         <v>77</v>
       </c>
       <c r="K181" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="L181" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="L181" t="s" s="2">
+      <c r="M181" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -23086,7 +23075,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-dmi-organization-interne.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-interne.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-organization-interne.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-interne.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6590" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1678,6 +1678,9 @@
   </si>
   <si>
     <t>Organization.type:TypeOrganizationInterne.coding.code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Organization.type:TypeOrganizationInterne.coding.display</t>
@@ -18388,7 +18391,7 @@
         <v>79</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>116</v>
@@ -18397,7 +18400,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18504,7 +18507,7 @@
         <v>79</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>99</v>
@@ -18730,7 +18733,7 @@
         <v>79</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>116</v>
@@ -18739,7 +18742,7 @@
         <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
@@ -18846,7 +18849,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -18960,7 +18963,7 @@
         <v>87</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>99</v>
@@ -19014,7 +19017,9 @@
       <c r="M146" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N146" s="2"/>
+      <c r="N146" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O146" t="s" s="2">
         <v>386</v>
       </c>
@@ -19074,7 +19079,7 @@
         <v>87</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>99</v>
@@ -19094,7 +19099,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>489</v>
@@ -19128,7 +19133,9 @@
       <c r="M147" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N147" s="2"/>
+      <c r="N147" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O147" t="s" s="2">
         <v>394</v>
       </c>
@@ -19188,7 +19195,7 @@
         <v>87</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19208,7 +19215,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>491</v>
@@ -19304,7 +19311,7 @@
         <v>87</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>99</v>
@@ -19324,7 +19331,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>493</v>
@@ -19420,7 +19427,7 @@
         <v>87</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>99</v>
@@ -19440,13 +19447,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>457</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>77</v>
@@ -19558,7 +19565,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>472</v>
@@ -19670,7 +19677,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>474</v>
@@ -19764,7 +19771,7 @@
         <v>79</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>116</v>
@@ -19773,7 +19780,7 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
@@ -19784,7 +19791,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>476</v>
@@ -19880,7 +19887,7 @@
         <v>79</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>99</v>
@@ -19900,7 +19907,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>478</v>
@@ -20012,7 +20019,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>480</v>
@@ -20106,7 +20113,7 @@
         <v>79</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>116</v>
@@ -20115,7 +20122,7 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
@@ -20126,7 +20133,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>482</v>
@@ -20174,7 +20181,7 @@
         <v>77</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>77</v>
@@ -20222,7 +20229,7 @@
         <v>87</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>99</v>
@@ -20242,7 +20249,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>484</v>
@@ -20336,7 +20343,7 @@
         <v>87</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>99</v>
@@ -20356,7 +20363,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>486</v>
@@ -20390,7 +20397,9 @@
       <c r="M158" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N158" s="2"/>
+      <c r="N158" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O158" t="s" s="2">
         <v>386</v>
       </c>
@@ -20450,7 +20459,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -20470,7 +20479,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>489</v>
@@ -20504,7 +20513,9 @@
       <c r="M159" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N159" s="2"/>
+      <c r="N159" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O159" t="s" s="2">
         <v>394</v>
       </c>
@@ -20564,7 +20575,7 @@
         <v>87</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>99</v>
@@ -20584,7 +20595,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>491</v>
@@ -20680,7 +20691,7 @@
         <v>87</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>99</v>
@@ -20700,7 +20711,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>493</v>
@@ -20796,7 +20807,7 @@
         <v>87</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>99</v>
@@ -20816,10 +20827,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20845,16 +20856,16 @@
         <v>101</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20903,7 +20914,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20918,13 +20929,13 @@
         <v>99</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>77</v>
@@ -20932,10 +20943,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20961,16 +20972,16 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -21019,7 +21030,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21037,7 +21048,7 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -21048,10 +21059,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21074,19 +21085,19 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21135,7 +21146,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21147,16 +21158,16 @@
         <v>199</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>77</v>
@@ -21164,10 +21175,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21190,19 +21201,19 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21251,7 +21262,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21263,16 +21274,16 @@
         <v>199</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>77</v>
@@ -21280,10 +21291,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21306,17 +21317,17 @@
         <v>88</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21365,7 +21376,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21383,7 +21394,7 @@
         <v>453</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>105</v>
@@ -21394,10 +21405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21506,10 +21517,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21620,10 +21631,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21649,13 +21660,13 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21705,7 +21716,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21714,7 +21725,7 @@
         <v>87</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>99</v>
@@ -21734,10 +21745,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21763,13 +21774,13 @@
         <v>129</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21817,7 +21828,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -21846,10 +21857,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21875,13 +21886,13 @@
         <v>229</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -21931,7 +21942,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21949,7 +21960,7 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
@@ -21960,10 +21971,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21989,13 +22000,13 @@
         <v>101</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22045,7 +22056,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22074,10 +22085,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22100,19 +22111,19 @@
         <v>77</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -22161,7 +22172,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22179,7 +22190,7 @@
         <v>77</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>77</v>
@@ -22190,10 +22201,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22302,10 +22313,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22416,14 +22427,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -22445,10 +22456,10 @@
         <v>108</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>111</v>
@@ -22503,7 +22514,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -22532,10 +22543,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22561,14 +22572,14 @@
         <v>252</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -22596,10 +22607,10 @@
         <v>149</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>77</v>
@@ -22617,7 +22628,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -22635,7 +22646,7 @@
         <v>77</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>77</v>
@@ -22646,10 +22657,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22672,17 +22683,17 @@
         <v>77</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>77</v>
@@ -22731,7 +22742,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -22746,10 +22757,10 @@
         <v>99</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>77</v>
@@ -22760,10 +22771,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22786,17 +22797,17 @@
         <v>77</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -22845,7 +22856,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -22857,16 +22868,16 @@
         <v>199</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>77</v>
@@ -22874,10 +22885,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22900,19 +22911,19 @@
         <v>77</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -22961,7 +22972,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -22976,13 +22987,13 @@
         <v>99</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>77</v>
@@ -22990,10 +23001,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23016,17 +23027,17 @@
         <v>77</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -23075,7 +23086,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
